--- a/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/1_four_bus_radial_1ph_grid_MP_pf_sc_results_0_bus.xlsx
+++ b/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/1_four_bus_radial_1ph_grid_MP_pf_sc_results_0_bus.xlsx
@@ -68,9 +68,6 @@
     <t>pf_va_degree</t>
   </si>
   <si>
-    <t>Bus_0</t>
-  </si>
-  <si>
     <t>Bus_1</t>
   </si>
   <si>
@@ -78,6 +75,9 @@
   </si>
   <si>
     <t>Bus_3</t>
+  </si>
+  <si>
+    <t>Bus_0</t>
   </si>
   <si>
     <t>pf_ikss_a_ka</t>
@@ -523,22 +523,22 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>144.3375636545937</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>99.99999896630133</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>0.0001671662503139904</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0.001671662470412813</v>
+        <v>0</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>84.28940675143633</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -592,22 +592,22 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>144.3375636545937</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>99.99999896630133</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>0.0001671662503139904</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>0.001671662470412813</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>84.28940675143633</v>
       </c>
     </row>
   </sheetData>
@@ -681,66 +681,66 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>125.00000523131</v>
+        <v>125.0000052313104</v>
       </c>
       <c r="D2">
-        <v>125.00000523131</v>
+        <v>125.0000052313104</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>28.86751509776008</v>
+        <v>28.86751509776017</v>
       </c>
       <c r="G2">
-        <v>28.86751509776008</v>
+        <v>28.86751509776017</v>
       </c>
       <c r="H2">
-        <v>0.0001751269027542989</v>
+        <v>0.0001751269027543618</v>
       </c>
       <c r="I2">
-        <v>0.001751267198644296</v>
+        <v>0.001751267198644409</v>
       </c>
       <c r="J2">
-        <v>0.0001751265479909091</v>
+        <v>0.0001751265479908494</v>
       </c>
       <c r="K2">
-        <v>0.001751265445205474</v>
+        <v>0.001751265445205304</v>
       </c>
       <c r="L2">
-        <v>0.0001751265479800903</v>
+        <v>0.0001751265479799772</v>
       </c>
       <c r="M2">
-        <v>0.001751265445186644</v>
+        <v>0.001751265445186629</v>
       </c>
       <c r="N2">
-        <v>0.9526279648091451</v>
+        <v>0.9526279648091419</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>0.9526279648092949</v>
+        <v>0.9526279648092906</v>
       </c>
       <c r="Q2">
-        <v>-6.112671398201336E-13</v>
+        <v>1.23183404586884E-13</v>
       </c>
       <c r="R2">
         <v>0</v>
       </c>
       <c r="S2">
-        <v>179.9999999999919</v>
+        <v>-179.9999999999925</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -779,27 +779,27 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9526279256079686</v>
+        <v>0.9526279256143186</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.9526280040104754</v>
+        <v>0.9526280040101338</v>
       </c>
       <c r="Q3">
-        <v>3.489807837214318E-06</v>
+        <v>3.489802277843601E-06</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>179.9999965101838</v>
+        <v>179.9999965106964</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -838,27 +838,27 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9526279125409111</v>
+        <v>0.952627912546729</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.9526280170775357</v>
+        <v>0.9526280170739052</v>
       </c>
       <c r="Q4">
-        <v>4.653077374358234E-06</v>
+        <v>4.652985918985988E-06</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.9999953469145</v>
+        <v>179.9999953474234</v>
       </c>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -897,22 +897,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9526279177677338</v>
+        <v>0.9526279177735119</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.9526280118507119</v>
+        <v>0.9526280118468633</v>
       </c>
       <c r="Q5">
-        <v>4.187769561068439E-06</v>
+        <v>4.187751579633669E-06</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9999958122222</v>
+        <v>179.9999958129363</v>
       </c>
     </row>
   </sheetData>
@@ -986,7 +986,7 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1007,22 +1007,22 @@
         <v>0.01371209888468002</v>
       </c>
       <c r="H2">
-        <v>0.0001671665735633938</v>
+        <v>0.0001671665735633701</v>
       </c>
       <c r="I2">
-        <v>0.001671664068087942</v>
+        <v>0.001671664068087988</v>
       </c>
       <c r="J2">
-        <v>0.0001671662503029855</v>
+        <v>0.0001671662503028824</v>
       </c>
       <c r="K2">
-        <v>0.001671662470403454</v>
+        <v>0.001671662470403327</v>
       </c>
       <c r="L2">
-        <v>0.0001671662503084033</v>
+        <v>0.000167166250308345</v>
       </c>
       <c r="M2">
-        <v>0.001671662470412751</v>
+        <v>0.001671662470412701</v>
       </c>
       <c r="N2">
         <v>1.050040161671014</v>
@@ -1045,7 +1045,7 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1084,27 +1084,27 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.050040161649228</v>
+        <v>1.050040161649227</v>
       </c>
       <c r="O3">
-        <v>1.04961389280142</v>
+        <v>1.049613892801414</v>
       </c>
       <c r="P3">
-        <v>1.049766722039164</v>
+        <v>1.049766722039159</v>
       </c>
       <c r="Q3">
-        <v>29.98657053591074</v>
+        <v>29.9865705359107</v>
       </c>
       <c r="R3">
-        <v>-90.0172339148521</v>
+        <v>-90.01723391485226</v>
       </c>
       <c r="S3">
-        <v>150.0048172592182</v>
+        <v>150.0048172592184</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1143,27 +1143,27 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.050040161641966</v>
+        <v>1.050040161641964</v>
       </c>
       <c r="O4">
-        <v>1.049613892807491</v>
+        <v>1.049613892807484</v>
       </c>
       <c r="P4">
-        <v>1.049766722049463</v>
+        <v>1.049766722049458</v>
       </c>
       <c r="Q4">
-        <v>29.98657053633082</v>
+        <v>29.98657053633075</v>
       </c>
       <c r="R4">
-        <v>-90.01723391374522</v>
+        <v>-90.01723391374537</v>
       </c>
       <c r="S4">
-        <v>150.0048172593512</v>
+        <v>150.0048172593514</v>
       </c>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1205,19 +1205,19 @@
         <v>1.05004016164487</v>
       </c>
       <c r="O5">
-        <v>1.049613892805062</v>
+        <v>1.049613892805056</v>
       </c>
       <c r="P5">
-        <v>1.049766722045343</v>
+        <v>1.049766722045336</v>
       </c>
       <c r="Q5">
-        <v>29.98657053616279</v>
+        <v>29.98657053616278</v>
       </c>
       <c r="R5">
-        <v>-90.01723391418797</v>
+        <v>-90.01723391418821</v>
       </c>
       <c r="S5">
-        <v>150.004817259298</v>
+        <v>150.0048172592982</v>
       </c>
     </row>
   </sheetData>
@@ -1291,13 +1291,13 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.0622014310633504</v>
+        <v>0.06220143106335042</v>
       </c>
       <c r="D2">
         <v>0.06220143106335042</v>
@@ -1312,22 +1312,22 @@
         <v>0.0143648054014144</v>
       </c>
       <c r="H2">
-        <v>0.0001751269027542989</v>
+        <v>0.0001751269027543618</v>
       </c>
       <c r="I2">
-        <v>0.001751267198644296</v>
+        <v>0.001751267198644409</v>
       </c>
       <c r="J2">
-        <v>0.0001751265479909091</v>
+        <v>0.0001751265479908494</v>
       </c>
       <c r="K2">
-        <v>0.001751265445205474</v>
+        <v>0.001751265445205304</v>
       </c>
       <c r="L2">
-        <v>0.0001751265479800903</v>
+        <v>0.0001751265479799772</v>
       </c>
       <c r="M2">
-        <v>0.001751265445186644</v>
+        <v>0.001751265445186629</v>
       </c>
       <c r="N2">
         <v>1.100044150706373</v>
@@ -1350,7 +1350,7 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1389,27 +1389,27 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.100044150682462</v>
+        <v>1.100044150682463</v>
       </c>
       <c r="O3">
-        <v>1.09957632624509</v>
+        <v>1.099576326245085</v>
       </c>
       <c r="P3">
-        <v>1.099744058336645</v>
+        <v>1.099744058336643</v>
       </c>
       <c r="Q3">
-        <v>29.98593127669038</v>
+        <v>29.98593127669026</v>
       </c>
       <c r="R3">
-        <v>-90.01805426134882</v>
+        <v>-90.01805426134894</v>
       </c>
       <c r="S3">
-        <v>150.0050468084502</v>
+        <v>150.0050468084504</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1448,19 +1448,19 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.100044150674492</v>
+        <v>1.100044150674491</v>
       </c>
       <c r="O4">
-        <v>1.099576326251752</v>
+        <v>1.099576326251746</v>
       </c>
       <c r="P4">
-        <v>1.099744058347948</v>
+        <v>1.099744058347945</v>
       </c>
       <c r="Q4">
-        <v>29.98593127713045</v>
+        <v>29.98593127713031</v>
       </c>
       <c r="R4">
-        <v>-90.01805426018922</v>
+        <v>-90.01805426018936</v>
       </c>
       <c r="S4">
         <v>150.0050468085896</v>
@@ -1468,7 +1468,7 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1507,22 +1507,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1.10004415067768</v>
+        <v>1.100044150677681</v>
       </c>
       <c r="O5">
-        <v>1.099576326249087</v>
+        <v>1.099576326249081</v>
       </c>
       <c r="P5">
-        <v>1.099744058343427</v>
+        <v>1.099744058343422</v>
       </c>
       <c r="Q5">
-        <v>29.98593127695441</v>
+        <v>29.98593127695435</v>
       </c>
       <c r="R5">
-        <v>-90.01805426065306</v>
+        <v>-90.01805426065327</v>
       </c>
       <c r="S5">
-        <v>150.0050468085338</v>
+        <v>150.005046808534</v>
       </c>
     </row>
   </sheetData>
@@ -1596,66 +1596,66 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>100.0000007626055</v>
+        <v>100.0000007626041</v>
       </c>
       <c r="D2">
-        <v>100.0000007626055</v>
+        <v>100.0000007626041</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>23.09401128782881</v>
+        <v>23.09401128782849</v>
       </c>
       <c r="G2">
-        <v>23.09401128782881</v>
+        <v>23.09401128782849</v>
       </c>
       <c r="H2">
-        <v>0.0001890574829298326</v>
+        <v>0.0001890574829297745</v>
       </c>
       <c r="I2">
-        <v>0.001890572694437162</v>
+        <v>0.001890572694437155</v>
       </c>
       <c r="J2">
-        <v>0.0001890570689231013</v>
+        <v>0.0001890570689231924</v>
       </c>
       <c r="K2">
-        <v>0.001890570651055411</v>
+        <v>0.00189057065105539</v>
       </c>
       <c r="L2">
-        <v>0.0001890570689138442</v>
+        <v>0.0001890570689138394</v>
       </c>
       <c r="M2">
-        <v>0.001890570651039279</v>
+        <v>0.001890570651039273</v>
       </c>
       <c r="N2">
-        <v>0.8227241232648949</v>
+        <v>0.8227241232649087</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>0.822724123265546</v>
+        <v>0.8227241232655603</v>
       </c>
       <c r="Q2">
-        <v>-2.12202491978381E-11</v>
+        <v>-2.039003878141915E-11</v>
       </c>
       <c r="R2">
         <v>0</v>
       </c>
       <c r="S2">
-        <v>-179.9999999999729</v>
+        <v>-179.9999999999721</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1694,27 +1694,27 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8227240894093462</v>
+        <v>0.8227240894151561</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.8227241571211057</v>
+        <v>0.8227241571330791</v>
       </c>
       <c r="Q3">
-        <v>6.700410056422599E-06</v>
+        <v>6.70003551251577E-06</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>179.9999932995818</v>
+        <v>179.9999932993478</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1753,27 +1753,27 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8227240781241666</v>
+        <v>0.8227240781308127</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.8227241684062941</v>
+        <v>0.8227241684206222</v>
       </c>
       <c r="Q4">
-        <v>8.93388721320405E-06</v>
+        <v>8.933575703532024E-06</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.9999910661051</v>
+        <v>179.9999910656533</v>
       </c>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1812,22 +1812,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8227240826382378</v>
+        <v>0.8227240826442416</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.822724163892219</v>
+        <v>0.8227241639057782</v>
       </c>
       <c r="Q5">
-        <v>8.04049637706469E-06</v>
+        <v>8.040217158420555E-06</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9999919594957</v>
+        <v>179.9999919591902</v>
       </c>
     </row>
   </sheetData>
@@ -1901,66 +1901,66 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>99.99999936827257</v>
+        <v>99.99999936826981</v>
       </c>
       <c r="D2">
-        <v>99.99999936827257</v>
+        <v>99.99999936826981</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>23.09401096582141</v>
+        <v>23.09401096582077</v>
       </c>
       <c r="G2">
-        <v>23.09401096582141</v>
+        <v>23.09401096582077</v>
       </c>
       <c r="H2">
-        <v>0.0001791070683994123</v>
+        <v>0.0001791070683994417</v>
       </c>
       <c r="I2">
-        <v>0.001791068766536983</v>
+        <v>0.001791068766536954</v>
       </c>
       <c r="J2">
-        <v>0.0001791066968295036</v>
+        <v>0.0001791066968295965</v>
       </c>
       <c r="K2">
-        <v>0.001791066932594685</v>
+        <v>0.00179106693259478</v>
       </c>
       <c r="L2">
-        <v>0.0001791066968172275</v>
+        <v>0.0001791066968171942</v>
       </c>
       <c r="M2">
-        <v>0.001791066932573329</v>
+        <v>0.001791066932573288</v>
       </c>
       <c r="N2">
-        <v>0.7794228427537606</v>
+        <v>0.7794228427537673</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>0.779422842754196</v>
+        <v>0.7794228427542037</v>
       </c>
       <c r="Q2">
-        <v>-2.492563970466476E-11</v>
+        <v>-2.460514403284443E-11</v>
       </c>
       <c r="R2">
         <v>0</v>
       </c>
       <c r="S2">
-        <v>-179.9999999999692</v>
+        <v>-179.9999999999688</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1999,27 +1999,27 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.7794228106800833</v>
+        <v>0.7794228106787265</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.7794228748278839</v>
+        <v>0.7794228748371319</v>
       </c>
       <c r="Q3">
-        <v>6.7004063560551E-06</v>
+        <v>6.699810544030828E-06</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>179.9999932995855</v>
+        <v>179.9999932997869</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2058,27 +2058,27 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.7794227999888608</v>
+        <v>0.7794227999869562</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.779422885519115</v>
+        <v>0.779422885528095</v>
       </c>
       <c r="Q4">
-        <v>8.933883505531306E-06</v>
+        <v>8.933316079021354E-06</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.9999910661088</v>
+        <v>179.9999910662885</v>
       </c>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2117,22 +2117,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.7794228042653493</v>
+        <v>0.7794228042641762</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.7794228812426227</v>
+        <v>0.7794228812533731</v>
       </c>
       <c r="Q5">
-        <v>8.040492672314043E-06</v>
+        <v>8.039992187547874E-06</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9999919594994</v>
+        <v>179.9999919596293</v>
       </c>
     </row>
   </sheetData>
@@ -2206,7 +2206,7 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2227,22 +2227,22 @@
         <v>0.01240558772539125</v>
       </c>
       <c r="H2">
-        <v>0.0001890574829298326</v>
+        <v>0.0001890574829297745</v>
       </c>
       <c r="I2">
-        <v>0.001890572694437162</v>
+        <v>0.001890572694437155</v>
       </c>
       <c r="J2">
-        <v>0.0001890570689231013</v>
+        <v>0.0001890570689231924</v>
       </c>
       <c r="K2">
-        <v>0.001890570651055411</v>
+        <v>0.00189057065105539</v>
       </c>
       <c r="L2">
-        <v>0.0001890570689138442</v>
+        <v>0.0001890570689138394</v>
       </c>
       <c r="M2">
-        <v>0.001890570651039279</v>
+        <v>0.001890570651039273</v>
       </c>
       <c r="N2">
         <v>0.9500411239734466</v>
@@ -2265,7 +2265,7 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2304,27 +2304,27 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9500411239471596</v>
+        <v>0.9500411239471629</v>
       </c>
       <c r="O3">
-        <v>0.9496049682109939</v>
+        <v>0.9496049682109926</v>
       </c>
       <c r="P3">
-        <v>0.9497613524775887</v>
+        <v>0.9497613524775911</v>
       </c>
       <c r="Q3">
-        <v>29.98481262681048</v>
+        <v>29.98481262681041</v>
       </c>
       <c r="R3">
         <v>-90.01948979669775</v>
       </c>
       <c r="S3">
-        <v>150.0054485531582</v>
+        <v>150.0054485531584</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2363,27 +2363,27 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.950041123938397</v>
+        <v>0.9500411239384</v>
       </c>
       <c r="O4">
-        <v>0.9496049682299836</v>
+        <v>0.949604968229984</v>
       </c>
       <c r="P4">
-        <v>0.949761352495847</v>
+        <v>0.9497613524958491</v>
       </c>
       <c r="Q4">
-        <v>29.98481262777688</v>
+        <v>29.98481262777686</v>
       </c>
       <c r="R4">
-        <v>-90.01948979481512</v>
+        <v>-90.0194897948151</v>
       </c>
       <c r="S4">
-        <v>150.0054485531323</v>
+        <v>150.0054485531324</v>
       </c>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2422,22 +2422,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9500411239419021</v>
+        <v>0.9500411239419065</v>
       </c>
       <c r="O5">
-        <v>0.9496049682223878</v>
+        <v>0.9496049682223869</v>
       </c>
       <c r="P5">
-        <v>0.9497613524885438</v>
+        <v>0.9497613524885463</v>
       </c>
       <c r="Q5">
-        <v>29.98481262739032</v>
+        <v>29.98481262739024</v>
       </c>
       <c r="R5">
-        <v>-90.01948979556818</v>
+        <v>-90.01948979556819</v>
       </c>
       <c r="S5">
-        <v>150.0054485531427</v>
+        <v>150.0054485531429</v>
       </c>
     </row>
   </sheetData>
@@ -2511,13 +2511,13 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.05089163194142327</v>
+        <v>0.05089163194142328</v>
       </c>
       <c r="D2">
         <v>0.05089163194142327</v>
@@ -2532,22 +2532,22 @@
         <v>0.01175291913548417</v>
       </c>
       <c r="H2">
-        <v>0.0001791070683994123</v>
+        <v>0.0001791070683994417</v>
       </c>
       <c r="I2">
-        <v>0.001791068766536983</v>
+        <v>0.001791068766536954</v>
       </c>
       <c r="J2">
-        <v>0.0001791066968295036</v>
+        <v>0.0001791066968295965</v>
       </c>
       <c r="K2">
-        <v>0.001791066932594685</v>
+        <v>0.00179106693259478</v>
       </c>
       <c r="L2">
-        <v>0.0001791066968172275</v>
+        <v>0.0001791066968171942</v>
       </c>
       <c r="M2">
-        <v>0.001791066932573329</v>
+        <v>0.001791066932573288</v>
       </c>
       <c r="N2">
         <v>0.9000368991846307</v>
@@ -2570,7 +2570,7 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2609,27 +2609,27 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9000368991610371</v>
+        <v>0.9000368991610377</v>
       </c>
       <c r="O3">
-        <v>0.8996454379311245</v>
+        <v>0.8996454379311181</v>
       </c>
       <c r="P3">
-        <v>0.8997857927144112</v>
+        <v>0.8997857927144114</v>
       </c>
       <c r="Q3">
-        <v>29.98561165662456</v>
+        <v>29.9856116566244</v>
       </c>
       <c r="R3">
-        <v>-90.018464422031</v>
+        <v>-90.01846442203093</v>
       </c>
       <c r="S3">
-        <v>150.0051615878767</v>
+        <v>150.0051615878771</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2668,27 +2668,27 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9000368991531726</v>
+        <v>0.9000368991531724</v>
       </c>
       <c r="O4">
-        <v>0.8996454379481684</v>
+        <v>0.8996454379481624</v>
       </c>
       <c r="P4">
-        <v>0.8997857927307984</v>
+        <v>0.8997857927307975</v>
       </c>
       <c r="Q4">
-        <v>29.9856116575401</v>
+        <v>29.98561165754003</v>
       </c>
       <c r="R4">
-        <v>-90.01846442024745</v>
+        <v>-90.01846442024738</v>
       </c>
       <c r="S4">
-        <v>150.0051615878521</v>
+        <v>150.0051615878525</v>
       </c>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2727,22 +2727,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9000368991563183</v>
+        <v>0.90003689915632</v>
       </c>
       <c r="O5">
-        <v>0.8996454379413508</v>
+        <v>0.8996454379413448</v>
       </c>
       <c r="P5">
-        <v>0.8997857927242436</v>
+        <v>0.8997857927242442</v>
       </c>
       <c r="Q5">
-        <v>29.98561165717388</v>
+        <v>29.98561165717373</v>
       </c>
       <c r="R5">
-        <v>-90.01846442096087</v>
+        <v>-90.01846442096083</v>
       </c>
       <c r="S5">
-        <v>150.005161587862</v>
+        <v>150.0051615878623</v>
       </c>
     </row>
   </sheetData>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
-        <v>144.3375172056695</v>
+        <v>144.3375172056674</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>33.3333222618474</v>
+        <v>33.33332226184692</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -2840,48 +2840,48 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0.0001671665735634006</v>
+        <v>0.0001671665735635415</v>
       </c>
       <c r="I2">
-        <v>0.001671664068087803</v>
+        <v>0.001671664068087729</v>
       </c>
       <c r="J2">
-        <v>0.0001671662503228816</v>
+        <v>0.0001671662503228442</v>
       </c>
       <c r="K2">
-        <v>0.001671662470412814</v>
+        <v>0.001671662470412908</v>
       </c>
       <c r="L2">
-        <v>0.0001671662503084166</v>
+        <v>0.0001671662503084005</v>
       </c>
       <c r="M2">
-        <v>0.001671662470412719</v>
+        <v>0.001671662470412762</v>
       </c>
       <c r="N2">
-        <v>0.606217835713192</v>
+        <v>0.6062178357132011</v>
       </c>
       <c r="O2">
-        <v>1.049999952314382</v>
+        <v>1.049999952314391</v>
       </c>
       <c r="P2">
-        <v>0.6062178696070256</v>
+        <v>0.6062178696070653</v>
       </c>
       <c r="Q2">
-        <v>59.99998310736071</v>
+        <v>59.99998310735795</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999636</v>
+        <v>-89.99999999999517</v>
       </c>
       <c r="S2">
-        <v>120.0000150431323</v>
+        <v>120.0000150431358</v>
       </c>
       <c r="T2">
-        <v>144.3375172056695</v>
+        <v>144.3375172056674</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2920,22 +2920,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.606217905109522</v>
+        <v>0.6062179051078571</v>
       </c>
       <c r="O3">
-        <v>1.049999952314382</v>
+        <v>1.049999952322695</v>
       </c>
       <c r="P3">
-        <v>0.6062178641647828</v>
+        <v>0.606217864180808</v>
       </c>
       <c r="Q3">
-        <v>59.99997991452685</v>
+        <v>59.9999799137962</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999985465</v>
       </c>
       <c r="S3">
-        <v>120.0000223197157</v>
+        <v>120.0000223197645</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -2943,7 +2943,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2982,22 +2982,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.6062179282416325</v>
+        <v>0.6062179282411533</v>
       </c>
       <c r="O4">
-        <v>1.049999952314383</v>
+        <v>1.049999952318394</v>
       </c>
       <c r="P4">
-        <v>0.6062178623507045</v>
+        <v>0.6062178623644782</v>
       </c>
       <c r="Q4">
-        <v>59.99997885024904</v>
+        <v>59.99997884953979</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999960771</v>
       </c>
       <c r="S4">
-        <v>120.0000247452435</v>
+        <v>120.0000247459523</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -3005,7 +3005,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -3044,22 +3044,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.6062179189887884</v>
+        <v>0.6062179189864662</v>
       </c>
       <c r="O5">
-        <v>1.049999952314382</v>
+        <v>1.049999952323529</v>
       </c>
       <c r="P5">
-        <v>0.6062178630763355</v>
+        <v>0.6062178630933081</v>
       </c>
       <c r="Q5">
-        <v>59.99997927596016</v>
+        <v>59.99997927515169</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999994374</v>
       </c>
       <c r="S5">
-        <v>120.0000237750324</v>
+        <v>120.0000237748932</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -3139,10 +3139,10 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
-        <v>144.3375246773876</v>
+        <v>144.3375246773875</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>33.33332398736682</v>
+        <v>33.3333239873668</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -3160,48 +3160,48 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0.0001751269027543064</v>
+        <v>0.0001751269027544995</v>
       </c>
       <c r="I2">
-        <v>0.001751267198644151</v>
+        <v>0.001751267198644107</v>
       </c>
       <c r="J2">
-        <v>0.0001751265479889132</v>
+        <v>0.0001751265479888371</v>
       </c>
       <c r="K2">
-        <v>0.001751265445186707</v>
+        <v>0.001751265445186812</v>
       </c>
       <c r="L2">
-        <v>0.0001751265479801042</v>
+        <v>0.000175126547980027</v>
       </c>
       <c r="M2">
-        <v>0.001751265445186609</v>
+        <v>0.001751265445186547</v>
       </c>
       <c r="N2">
-        <v>0.6350853983254572</v>
+        <v>0.6350853983254513</v>
       </c>
       <c r="O2">
-        <v>1.100000023837893</v>
+        <v>1.100000023837902</v>
       </c>
       <c r="P2">
-        <v>0.6350854355226713</v>
+        <v>0.6350854355227258</v>
       </c>
       <c r="Q2">
-        <v>59.9999823030783</v>
+        <v>59.99998230307486</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999636</v>
+        <v>-89.99999999999518</v>
       </c>
       <c r="S2">
-        <v>120.0000157594195</v>
+        <v>120.0000157594221</v>
       </c>
       <c r="T2">
-        <v>144.3375246773876</v>
+        <v>144.3375246773875</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -3240,22 +3240,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.6350854710263789</v>
+        <v>0.6350854710164006</v>
       </c>
       <c r="O3">
-        <v>1.100000023837893</v>
+        <v>1.100000023845902</v>
       </c>
       <c r="P3">
-        <v>0.635085429821275</v>
+        <v>0.6350854298410954</v>
       </c>
       <c r="Q3">
-        <v>59.99997911024459</v>
+        <v>59.99997910956991</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999636</v>
+        <v>-89.99999999984853</v>
       </c>
       <c r="S3">
-        <v>120.0000230360027</v>
+        <v>120.0000230354209</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -3263,7 +3263,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -3302,22 +3302,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.6350854952600197</v>
+        <v>0.6350854952512834</v>
       </c>
       <c r="O4">
-        <v>1.100000023837893</v>
+        <v>1.100000023844556</v>
       </c>
       <c r="P4">
-        <v>0.6350854279208121</v>
+        <v>0.6350854279394532</v>
       </c>
       <c r="Q4">
-        <v>59.99997804596682</v>
+        <v>59.99997804531361</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999636</v>
+        <v>-89.99999999976383</v>
       </c>
       <c r="S4">
-        <v>120.0000254615305</v>
+        <v>120.0000254612227</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -3325,7 +3325,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -3364,22 +3364,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.6350854855665635</v>
+        <v>0.6350854855558966</v>
       </c>
       <c r="O5">
-        <v>1.100000023837893</v>
+        <v>1.100000023846776</v>
       </c>
       <c r="P5">
-        <v>0.6350854286809969</v>
+        <v>0.63508542870181</v>
       </c>
       <c r="Q5">
-        <v>59.99997847167793</v>
+        <v>59.99997847092545</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999636</v>
+        <v>-89.99999999993761</v>
       </c>
       <c r="S5">
-        <v>120.0000244913194</v>
+        <v>120.0000244905496</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -3459,7 +3459,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0.03428655025312638</v>
@@ -3480,22 +3480,22 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0.0001671665735634006</v>
+        <v>0.0001671665735635415</v>
       </c>
       <c r="I2">
-        <v>0.001671664068087803</v>
+        <v>0.001671664068087729</v>
       </c>
       <c r="J2">
-        <v>0.0001671662503228816</v>
+        <v>0.0001671662503228442</v>
       </c>
       <c r="K2">
-        <v>0.001671662470412814</v>
+        <v>0.001671662470412908</v>
       </c>
       <c r="L2">
-        <v>0.0001671662503084166</v>
+        <v>0.0001671662503084005</v>
       </c>
       <c r="M2">
-        <v>0.001671662470412719</v>
+        <v>0.001671662470412762</v>
       </c>
       <c r="N2">
         <v>1.049857834092781</v>
@@ -3521,7 +3521,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -3563,19 +3563,19 @@
         <v>1.049857834106118</v>
       </c>
       <c r="O3">
-        <v>1.049999952316283</v>
+        <v>1.049999952316284</v>
       </c>
       <c r="P3">
-        <v>1.049949014168014</v>
+        <v>1.049949014168016</v>
       </c>
       <c r="Q3">
-        <v>29.9987325629452</v>
+        <v>29.99873256294508</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999999636</v>
       </c>
       <c r="S3">
-        <v>149.9926499517085</v>
+        <v>149.9926499517083</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -3583,7 +3583,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -3625,19 +3625,19 @@
         <v>1.049857834110564</v>
       </c>
       <c r="O4">
-        <v>1.049999952316283</v>
+        <v>1.049999952316284</v>
       </c>
       <c r="P4">
-        <v>1.049949014166605</v>
+        <v>1.049949014166607</v>
       </c>
       <c r="Q4">
-        <v>29.99873256317405</v>
+        <v>29.99873256317392</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999999633</v>
       </c>
       <c r="S4">
-        <v>149.992649952033</v>
+        <v>149.9926499520329</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -3645,7 +3645,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -3684,22 +3684,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1.049857834108786</v>
+        <v>1.049857834108785</v>
       </c>
       <c r="O5">
-        <v>1.049999952316283</v>
+        <v>1.049999952316284</v>
       </c>
       <c r="P5">
-        <v>1.049949014167168</v>
+        <v>1.04994901416717</v>
       </c>
       <c r="Q5">
-        <v>29.99873256308251</v>
+        <v>29.99873256308239</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999999638</v>
       </c>
       <c r="S5">
-        <v>149.9926499519032</v>
+        <v>149.992649951903</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -3740,7 +3740,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>144.3375733382017</v>
@@ -3763,7 +3763,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -3786,7 +3786,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -3809,7 +3809,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -3904,7 +3904,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0.03591893103212428</v>
@@ -3925,22 +3925,22 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0.0001751269027543064</v>
+        <v>0.0001751269027544995</v>
       </c>
       <c r="I2">
-        <v>0.001751267198644151</v>
+        <v>0.001751267198644107</v>
       </c>
       <c r="J2">
-        <v>0.0001751265479889132</v>
+        <v>0.0001751265479888371</v>
       </c>
       <c r="K2">
-        <v>0.001751265445186707</v>
+        <v>0.001751265445186812</v>
       </c>
       <c r="L2">
-        <v>0.0001751265479801042</v>
+        <v>0.000175126547980027</v>
       </c>
       <c r="M2">
-        <v>0.001751265445186609</v>
+        <v>0.001751265445186547</v>
       </c>
       <c r="N2">
         <v>1.099844049471989</v>
@@ -3966,7 +3966,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -4005,22 +4005,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.099844049486628</v>
+        <v>1.099844049486627</v>
       </c>
       <c r="O3">
         <v>1.100000023841857</v>
       </c>
       <c r="P3">
-        <v>1.099944118813847</v>
+        <v>1.09994411881385</v>
       </c>
       <c r="Q3">
-        <v>29.99867227005884</v>
+        <v>29.9986722700586</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999999639</v>
       </c>
       <c r="S3">
-        <v>149.9923000198959</v>
+        <v>149.9923000198957</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -4028,7 +4028,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -4067,22 +4067,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.099844049491507</v>
+        <v>1.099844049491506</v>
       </c>
       <c r="O4">
         <v>1.100000023841857</v>
       </c>
       <c r="P4">
-        <v>1.099944118812301</v>
+        <v>1.099944118812304</v>
       </c>
       <c r="Q4">
-        <v>29.99867227029858</v>
+        <v>29.99867227029833</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999999638</v>
       </c>
       <c r="S4">
-        <v>149.9923000202358</v>
+        <v>149.9923000202357</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -4090,7 +4090,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -4129,22 +4129,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1.099844049489555</v>
+        <v>1.099844049489554</v>
       </c>
       <c r="O5">
         <v>1.100000023841857</v>
       </c>
       <c r="P5">
-        <v>1.099944118812919</v>
+        <v>1.099944118812922</v>
       </c>
       <c r="Q5">
-        <v>29.99867227020269</v>
+        <v>29.99867227020244</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999635</v>
+        <v>-89.9999999999964</v>
       </c>
       <c r="S5">
-        <v>149.9923000200999</v>
+        <v>149.9923000200996</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -4224,10 +4224,10 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
-        <v>115.4700126952653</v>
+        <v>115.4700126952659</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -4236,7 +4236,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>26.66665756254053</v>
+        <v>26.66665756254066</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -4245,48 +4245,48 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0.0001890574829298401</v>
+        <v>0.000189057482929753</v>
       </c>
       <c r="I2">
-        <v>0.001890572694437005</v>
+        <v>0.001890572694437055</v>
       </c>
       <c r="J2">
-        <v>0.0001890570689061108</v>
+        <v>0.0001890570689060227</v>
       </c>
       <c r="K2">
-        <v>0.001890570651039348</v>
+        <v>0.001890570651039273</v>
       </c>
       <c r="L2">
-        <v>0.00018905706891386</v>
+        <v>0.0001890570689138686</v>
       </c>
       <c r="M2">
-        <v>0.00189057065103924</v>
+        <v>0.001890570651039255</v>
       </c>
       <c r="N2">
-        <v>0.5484828312677188</v>
+        <v>0.5484828312677271</v>
       </c>
       <c r="O2">
-        <v>0.94999998807754</v>
+        <v>0.9499999880775428</v>
       </c>
       <c r="P2">
-        <v>0.548482866039011</v>
+        <v>0.5484828660390111</v>
       </c>
       <c r="Q2">
-        <v>59.99998089303169</v>
+        <v>59.99998089303069</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999636</v>
+        <v>-89.99999999999714</v>
       </c>
       <c r="S2">
-        <v>120.0000170098564</v>
+        <v>120.0000170098563</v>
       </c>
       <c r="T2">
-        <v>115.4700126952653</v>
+        <v>115.4700126952659</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -4325,22 +4325,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.5484829206719503</v>
+        <v>0.5484829206611916</v>
       </c>
       <c r="O3">
-        <v>0.94999998807754</v>
+        <v>0.9499999880718184</v>
       </c>
       <c r="P3">
-        <v>0.5484828877321672</v>
+        <v>0.5484828877326473</v>
       </c>
       <c r="Q3">
-        <v>59.99997288426815</v>
+        <v>59.99997288399845</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999636</v>
+        <v>-90.00000000025931</v>
       </c>
       <c r="S3">
-        <v>120.0000291023689</v>
+        <v>120.0000291014349</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -4348,7 +4348,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -4387,22 +4387,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.5484829504733617</v>
+        <v>0.5484829504639955</v>
       </c>
       <c r="O4">
-        <v>0.94999998807754</v>
+        <v>0.9499999880717798</v>
       </c>
       <c r="P4">
-        <v>0.5484828949632249</v>
+        <v>0.5484828949622326</v>
       </c>
       <c r="Q4">
-        <v>59.99997021468094</v>
+        <v>59.99997021435565</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999636</v>
+        <v>-90.0000000004045</v>
       </c>
       <c r="S4">
-        <v>120.0000331332061</v>
+        <v>120.0000331322101</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -4410,7 +4410,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -4449,22 +4449,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.5484829385527976</v>
+        <v>0.5484829385431584</v>
       </c>
       <c r="O5">
-        <v>0.94999998807754</v>
+        <v>0.9499999880737752</v>
       </c>
       <c r="P5">
-        <v>0.5484828920708015</v>
+        <v>0.5484828920716933</v>
       </c>
       <c r="Q5">
-        <v>59.99997128251577</v>
+        <v>59.99997128192832</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999636</v>
+        <v>-90.00000000066429</v>
       </c>
       <c r="S5">
-        <v>120.0000315208713</v>
+        <v>120.0000315194878</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -4544,10 +4544,10 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
-        <v>115.4700132967334</v>
+        <v>115.4700132967355</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -4556,7 +4556,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>26.66665770144365</v>
+        <v>26.66665770144411</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -4565,48 +4565,48 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0.0001791070683994198</v>
+        <v>0.0001791070683993362</v>
       </c>
       <c r="I2">
-        <v>0.001791068766536834</v>
+        <v>0.001791068766536804</v>
       </c>
       <c r="J2">
-        <v>0.0001791066968365459</v>
+        <v>0.0001791066968364573</v>
       </c>
       <c r="K2">
-        <v>0.001791066932573394</v>
+        <v>0.001791066932573339</v>
       </c>
       <c r="L2">
-        <v>0.0001791066968172419</v>
+        <v>0.0001791066968172345</v>
       </c>
       <c r="M2">
-        <v>0.001791066932573293</v>
+        <v>0.001791066932573301</v>
       </c>
       <c r="N2">
-        <v>0.5196153024775004</v>
+        <v>0.5196153024775132</v>
       </c>
       <c r="O2">
-        <v>0.8999999761583428</v>
+        <v>0.8999999761583425</v>
       </c>
       <c r="P2">
-        <v>0.5196153336893283</v>
+        <v>0.519615333689312</v>
       </c>
       <c r="Q2">
-        <v>59.99998189841276</v>
+        <v>59.99998189841345</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999635</v>
+        <v>-89.9999999999969</v>
       </c>
       <c r="S2">
         <v>120.0000161145722</v>
       </c>
       <c r="T2">
-        <v>115.4700132967334</v>
+        <v>115.4700132967355</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -4645,22 +4645,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.519615387176245</v>
+        <v>0.5196153871718352</v>
       </c>
       <c r="O3">
-        <v>0.8999999761583428</v>
+        <v>0.8999999761537597</v>
       </c>
       <c r="P3">
-        <v>0.5196153542407381</v>
+        <v>0.5196153542414281</v>
       </c>
       <c r="Q3">
-        <v>59.99997388964883</v>
+        <v>59.99997388921331</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999635</v>
+        <v>-90.0000000001194</v>
       </c>
       <c r="S3">
-        <v>120.0000282070852</v>
+        <v>120.0000282069499</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -4668,7 +4668,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -4707,22 +4707,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.5196154154091609</v>
+        <v>0.5196154154073164</v>
       </c>
       <c r="O4">
-        <v>0.8999999761583428</v>
+        <v>0.8999999761537885</v>
       </c>
       <c r="P4">
-        <v>0.5196153610912133</v>
+        <v>0.5196153610929011</v>
       </c>
       <c r="Q4">
-        <v>59.99997122006148</v>
+        <v>59.99997121945268</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999635</v>
+        <v>-90.00000000000549</v>
       </c>
       <c r="S4">
-        <v>120.0000322379224</v>
+        <v>120.0000322382881</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -4730,7 +4730,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -4769,22 +4769,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.5196154041159949</v>
+        <v>0.5196154041126455</v>
       </c>
       <c r="O5">
-        <v>0.8999999761583428</v>
+        <v>0.8999999761556134</v>
       </c>
       <c r="P5">
-        <v>0.5196153583510229</v>
+        <v>0.519615358352103</v>
       </c>
       <c r="Q5">
-        <v>59.99997228789635</v>
+        <v>59.99997228714308</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999635</v>
+        <v>-90.00000000052437</v>
       </c>
       <c r="S5">
-        <v>120.0000306255876</v>
+        <v>120.0000306250028</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -4864,7 +4864,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0.03102041860452112</v>
@@ -4885,22 +4885,22 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0.0001890574829298401</v>
+        <v>0.000189057482929753</v>
       </c>
       <c r="I2">
-        <v>0.001890572694437005</v>
+        <v>0.001890572694437055</v>
       </c>
       <c r="J2">
-        <v>0.0001890570689061108</v>
+        <v>0.0001890570689060227</v>
       </c>
       <c r="K2">
-        <v>0.001890570651039348</v>
+        <v>0.001890570651039273</v>
       </c>
       <c r="L2">
-        <v>0.00018905706891386</v>
+        <v>0.0001890570689138686</v>
       </c>
       <c r="M2">
-        <v>0.00189057065103924</v>
+        <v>0.001890570651039255</v>
       </c>
       <c r="N2">
         <v>0.9498545697172979</v>
@@ -4926,7 +4926,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -4968,19 +4968,19 @@
         <v>0.9498545697450591</v>
       </c>
       <c r="O3">
-        <v>0.949999988079071</v>
+        <v>0.9499999880790718</v>
       </c>
       <c r="P3">
-        <v>0.94994786569568</v>
+        <v>0.9499478656956807</v>
       </c>
       <c r="Q3">
-        <v>29.99856677104417</v>
+        <v>29.99856677104404</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999999645</v>
       </c>
       <c r="S3">
-        <v>149.9916876554471</v>
+        <v>149.9916876554469</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -4988,7 +4988,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -5027,22 +5027,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9498545697543129</v>
+        <v>0.949854569754313</v>
       </c>
       <c r="O4">
-        <v>0.949999988079071</v>
+        <v>0.9499999880790718</v>
       </c>
       <c r="P4">
         <v>0.949947865695924</v>
       </c>
       <c r="Q4">
-        <v>29.99856677134935</v>
+        <v>29.99856677134925</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999999648</v>
       </c>
       <c r="S4">
-        <v>149.991687656083</v>
+        <v>149.9916876560829</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -5050,7 +5050,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -5089,22 +5089,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9498545697506113</v>
+        <v>0.949854569750612</v>
       </c>
       <c r="O5">
-        <v>0.949999988079071</v>
+        <v>0.9499999880790728</v>
       </c>
       <c r="P5">
-        <v>0.9499478656958263</v>
+        <v>0.9499478656958273</v>
       </c>
       <c r="Q5">
-        <v>29.99856677122727</v>
+        <v>29.99856677122711</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999999653</v>
       </c>
       <c r="S5">
-        <v>149.9916876558286</v>
+        <v>149.9916876558284</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -5184,7 +5184,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0.02938808622558128</v>
@@ -5205,22 +5205,22 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0.0001791070683994198</v>
+        <v>0.0001791070683993362</v>
       </c>
       <c r="I2">
-        <v>0.001791068766536834</v>
+        <v>0.001791068766536804</v>
       </c>
       <c r="J2">
-        <v>0.0001791066968365459</v>
+        <v>0.0001791066968364573</v>
       </c>
       <c r="K2">
-        <v>0.001791066932573394</v>
+        <v>0.001791066932573339</v>
       </c>
       <c r="L2">
-        <v>0.0001791066968172419</v>
+        <v>0.0001791066968172345</v>
       </c>
       <c r="M2">
-        <v>0.001791066932573293</v>
+        <v>0.001791066932573301</v>
       </c>
       <c r="N2">
         <v>0.8998694609216684</v>
@@ -5246,7 +5246,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -5285,22 +5285,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8998694609465844</v>
+        <v>0.8998694609465853</v>
       </c>
       <c r="O3">
-        <v>0.8999999761581415</v>
+        <v>0.8999999761581422</v>
       </c>
       <c r="P3">
-        <v>0.8999531960818978</v>
+        <v>0.8999531960818993</v>
       </c>
       <c r="Q3">
-        <v>29.99864212583539</v>
+        <v>29.99864212583526</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999999643</v>
       </c>
       <c r="S3">
-        <v>149.9921250571565</v>
+        <v>149.9921250571564</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -5308,7 +5308,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -5347,19 +5347,19 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8998694609548898</v>
+        <v>0.8998694609548912</v>
       </c>
       <c r="O4">
-        <v>0.8999999761581415</v>
+        <v>0.8999999761581414</v>
       </c>
       <c r="P4">
-        <v>0.899953196082117</v>
+        <v>0.8999531960821187</v>
       </c>
       <c r="Q4">
-        <v>29.99864212612451</v>
+        <v>29.99864212612438</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999635</v>
+        <v>-89.9999999999964</v>
       </c>
       <c r="S4">
         <v>149.992125057759</v>
@@ -5370,7 +5370,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -5409,22 +5409,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8998694609515677</v>
+        <v>0.8998694609515691</v>
       </c>
       <c r="O5">
-        <v>0.8999999761581415</v>
+        <v>0.8999999761581431</v>
       </c>
       <c r="P5">
-        <v>0.8999531960820293</v>
+        <v>0.8999531960820309</v>
       </c>
       <c r="Q5">
-        <v>29.99864212600886</v>
+        <v>29.9986421260087</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999635</v>
+        <v>-89.9999999999965</v>
       </c>
       <c r="S5">
-        <v>149.992125057518</v>
+        <v>149.9921250575179</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -5504,69 +5504,69 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>144.3375444656639</v>
+        <v>144.3375444656649</v>
       </c>
       <c r="D2">
-        <v>144.3375363964254</v>
+        <v>144.3375363964234</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>33.33332855727355</v>
+        <v>33.33332855727378</v>
       </c>
       <c r="G2">
-        <v>33.33332669376271</v>
+        <v>33.33332669376225</v>
       </c>
       <c r="H2">
-        <v>0.0001671665735633938</v>
+        <v>0.0001671665735633701</v>
       </c>
       <c r="I2">
-        <v>0.001671664068087942</v>
+        <v>0.001671664068087988</v>
       </c>
       <c r="J2">
-        <v>0.0001671662503029855</v>
+        <v>0.0001671662503028824</v>
       </c>
       <c r="K2">
-        <v>0.001671662470403454</v>
+        <v>0.001671662470403327</v>
       </c>
       <c r="L2">
-        <v>0.0001671662503084033</v>
+        <v>0.000167166250308345</v>
       </c>
       <c r="M2">
-        <v>0.001671662470412751</v>
+        <v>0.001671662470412701</v>
       </c>
       <c r="N2">
-        <v>0.6062179502088811</v>
+        <v>0.6062179502088497</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>0.6062179502068222</v>
+        <v>0.6062179502068165</v>
       </c>
       <c r="Q2">
-        <v>-1.84939574532222E-06</v>
+        <v>-1.849392855963534E-06</v>
       </c>
       <c r="R2">
         <v>0</v>
       </c>
       <c r="S2">
-        <v>179.9999981506067</v>
+        <v>179.9999981506099</v>
       </c>
       <c r="T2">
-        <v>144.33747075766</v>
+        <v>144.3374707576572</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -5605,22 +5605,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.6062179447665949</v>
+        <v>0.6062179447710628</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.6062180196031437</v>
+        <v>0.6062180195985242</v>
       </c>
       <c r="Q3">
-        <v>5.427187866450479E-06</v>
+        <v>5.427749614995383E-06</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>179.9999949577693</v>
+        <v>179.9999949594123</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -5628,7 +5628,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -5667,22 +5667,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.6062179429525018</v>
+        <v>0.6062179429577668</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.6062180427352506</v>
+        <v>0.6062180427264563</v>
       </c>
       <c r="Q4">
-        <v>7.852715730704622E-06</v>
+        <v>7.85341020113607E-06</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.9999938934903</v>
+        <v>179.9999938952324</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -5690,7 +5690,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -5729,22 +5729,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.6062179436781385</v>
+        <v>0.6062179436814714</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.6062180334824081</v>
+        <v>0.606218033475812</v>
       </c>
       <c r="Q5">
-        <v>6.882504611127791E-06</v>
+        <v>6.883072487507427E-06</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9999943192019</v>
+        <v>179.9999943212487</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -5824,69 +5824,69 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>144.3375532343171</v>
+        <v>144.3375532343185</v>
       </c>
       <c r="D2">
-        <v>144.337544780828</v>
+        <v>144.3375447808261</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>33.33333058230729</v>
+        <v>33.33333058230762</v>
       </c>
       <c r="G2">
-        <v>33.33332863005758</v>
+        <v>33.33332863005714</v>
       </c>
       <c r="H2">
-        <v>0.0001751269027542989</v>
+        <v>0.0001751269027543618</v>
       </c>
       <c r="I2">
-        <v>0.001751267198644296</v>
+        <v>0.001751267198644409</v>
       </c>
       <c r="J2">
-        <v>0.0001751265479909091</v>
+        <v>0.0001751265479908494</v>
       </c>
       <c r="K2">
-        <v>0.001751265445205474</v>
+        <v>0.001751265445205304</v>
       </c>
       <c r="L2">
-        <v>0.0001751265479800903</v>
+        <v>0.0001751265479799772</v>
       </c>
       <c r="M2">
-        <v>0.001751265445186644</v>
+        <v>0.001751265445186629</v>
       </c>
       <c r="N2">
-        <v>0.6350855239800868</v>
+        <v>0.6350855239800861</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>0.6350855239766456</v>
+        <v>0.6350855239766665</v>
       </c>
       <c r="Q2">
-        <v>-1.937573058844578E-06</v>
+        <v>-1.93757031810418E-06</v>
       </c>
       <c r="R2">
         <v>0</v>
       </c>
       <c r="S2">
-        <v>179.9999980625901</v>
+        <v>179.9999980625932</v>
       </c>
       <c r="T2">
-        <v>144.3374760164012</v>
+        <v>144.337476016397</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -5925,22 +5925,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.635085518278642</v>
+        <v>0.6350855182899039</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.6350855966775578</v>
+        <v>0.6350855966798077</v>
       </c>
       <c r="Q3">
-        <v>5.339010388924446E-06</v>
+        <v>5.339094682509593E-06</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>179.9999948697527</v>
+        <v>179.9999948706365</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -5948,7 +5948,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -5987,22 +5987,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.6350855163781634</v>
+        <v>0.6350855163904218</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.6350856209111949</v>
+        <v>0.6350856209103294</v>
       </c>
       <c r="Q4">
-        <v>7.764538193377832E-06</v>
+        <v>7.764765077483799E-06</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.9999938054737</v>
+        <v>179.9999938065837</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -6010,7 +6010,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -6049,22 +6049,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.6350855171383544</v>
+        <v>0.6350855171484269</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.6350856112177403</v>
+        <v>0.6350856112179195</v>
       </c>
       <c r="Q5">
-        <v>6.794327097611475E-06</v>
+        <v>6.794417527062807E-06</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9999942311852</v>
+        <v>179.9999942324729</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -6144,13 +6144,13 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.03428655025296316</v>
+        <v>0.03428655025296317</v>
       </c>
       <c r="D2">
         <v>0.03428655025548489</v>
@@ -6159,28 +6159,28 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.007918139725242239</v>
+        <v>0.007918139725242242</v>
       </c>
       <c r="G2">
         <v>0.007918139725824608</v>
       </c>
       <c r="H2">
-        <v>0.0001671665735633938</v>
+        <v>0.0001671665735633701</v>
       </c>
       <c r="I2">
-        <v>0.001671664068087942</v>
+        <v>0.001671664068087988</v>
       </c>
       <c r="J2">
-        <v>0.0001671662503029855</v>
+        <v>0.0001671662503028824</v>
       </c>
       <c r="K2">
-        <v>0.001671662470403454</v>
+        <v>0.001671662470403327</v>
       </c>
       <c r="L2">
-        <v>0.0001671662503084033</v>
+        <v>0.000167166250308345</v>
       </c>
       <c r="M2">
-        <v>0.001671662470412751</v>
+        <v>0.001671662470412701</v>
       </c>
       <c r="N2">
         <v>1.049949014172255</v>
@@ -6201,12 +6201,12 @@
         <v>149.998732562254</v>
       </c>
       <c r="T2">
-        <v>0.03428655025093119</v>
+        <v>0.03428655025093121</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -6245,22 +6245,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.049949014168027</v>
+        <v>1.049949014168029</v>
       </c>
       <c r="O3">
-        <v>1.049806898938646</v>
+        <v>1.049806898938644</v>
       </c>
       <c r="P3">
-        <v>1.04985783410611</v>
+        <v>1.049857834106109</v>
       </c>
       <c r="Q3">
-        <v>29.99264995171317</v>
+        <v>29.99264995171307</v>
       </c>
       <c r="R3">
-        <v>-90.00861854183903</v>
+        <v>-90.00861854183921</v>
       </c>
       <c r="S3">
-        <v>149.9987325629405</v>
+        <v>149.9987325629406</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -6268,7 +6268,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -6307,22 +6307,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.049949014166618</v>
+        <v>1.04994901416662</v>
       </c>
       <c r="O4">
-        <v>1.049806898941682</v>
+        <v>1.049806898941679</v>
       </c>
       <c r="P4">
-        <v>1.049857834110556</v>
+        <v>1.049857834110554</v>
       </c>
       <c r="Q4">
-        <v>29.99264995203768</v>
+        <v>29.99264995203758</v>
       </c>
       <c r="R4">
-        <v>-90.00861854128557</v>
+        <v>-90.0086185412858</v>
       </c>
       <c r="S4">
-        <v>149.9987325631694</v>
+        <v>149.9987325631695</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -6330,7 +6330,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -6369,22 +6369,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1.049949014167182</v>
+        <v>1.049949014167184</v>
       </c>
       <c r="O5">
-        <v>1.049806898940467</v>
+        <v>1.049806898940465</v>
       </c>
       <c r="P5">
-        <v>1.049857834108778</v>
+        <v>1.049857834108775</v>
       </c>
       <c r="Q5">
-        <v>29.99264995190788</v>
+        <v>29.99264995190779</v>
       </c>
       <c r="R5">
-        <v>-90.00861854150695</v>
+        <v>-90.00861854150719</v>
       </c>
       <c r="S5">
-        <v>149.9987325630778</v>
+        <v>149.9987325630779</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -6464,7 +6464,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -6485,22 +6485,22 @@
         <v>0.008295121924393387</v>
       </c>
       <c r="H2">
-        <v>0.0001751269027542989</v>
+        <v>0.0001751269027543618</v>
       </c>
       <c r="I2">
-        <v>0.001751267198644296</v>
+        <v>0.001751267198644409</v>
       </c>
       <c r="J2">
-        <v>0.0001751265479909091</v>
+        <v>0.0001751265479908494</v>
       </c>
       <c r="K2">
-        <v>0.001751265445205474</v>
+        <v>0.001751265445205304</v>
       </c>
       <c r="L2">
-        <v>0.0001751265479800903</v>
+        <v>0.0001751265479799772</v>
       </c>
       <c r="M2">
-        <v>0.001751265445186644</v>
+        <v>0.001751265445186629</v>
       </c>
       <c r="N2">
         <v>1.0999441188185</v>
@@ -6526,7 +6526,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -6565,19 +6565,19 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.09994411881386</v>
+        <v>1.099944118813863</v>
       </c>
       <c r="O3">
-        <v>1.099788147885714</v>
+        <v>1.099788147885713</v>
       </c>
       <c r="P3">
-        <v>1.099844049486614</v>
+        <v>1.099844049486616</v>
       </c>
       <c r="Q3">
-        <v>29.99230001990052</v>
+        <v>29.99230001990036</v>
       </c>
       <c r="R3">
-        <v>-90.00902886954131</v>
+        <v>-90.00902886954145</v>
       </c>
       <c r="S3">
         <v>149.9986722700542</v>
@@ -6588,7 +6588,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -6627,22 +6627,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.099944118812313</v>
+        <v>1.099944118812316</v>
       </c>
       <c r="O4">
-        <v>1.099788147889046</v>
+        <v>1.099788147889045</v>
       </c>
       <c r="P4">
-        <v>1.099844049491494</v>
+        <v>1.099844049491495</v>
       </c>
       <c r="Q4">
-        <v>29.99230002024049</v>
+        <v>29.99230002024031</v>
       </c>
       <c r="R4">
-        <v>-90.00902886896152</v>
+        <v>-90.00902886896168</v>
       </c>
       <c r="S4">
-        <v>149.9986722702939</v>
+        <v>149.998672270294</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -6650,7 +6650,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -6689,22 +6689,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1.099944118812932</v>
+        <v>1.099944118812935</v>
       </c>
       <c r="O5">
-        <v>1.099788147887713</v>
+        <v>1.099788147887712</v>
       </c>
       <c r="P5">
         <v>1.099844049489542</v>
       </c>
       <c r="Q5">
-        <v>29.9923000201045</v>
+        <v>29.99230002010435</v>
       </c>
       <c r="R5">
-        <v>-90.00902886919343</v>
+        <v>-90.00902886919361</v>
       </c>
       <c r="S5">
-        <v>149.998672270198</v>
+        <v>149.9986722701981</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -6784,69 +6784,69 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>115.470037366769</v>
+        <v>115.4700373667703</v>
       </c>
       <c r="D2">
-        <v>115.4700300462335</v>
+        <v>115.4700300462329</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>26.66666326018035</v>
+        <v>26.66666326018064</v>
       </c>
       <c r="G2">
-        <v>26.66666156957506</v>
+        <v>26.66666156957491</v>
       </c>
       <c r="H2">
-        <v>0.0001890574829298326</v>
+        <v>0.0001890574829297745</v>
       </c>
       <c r="I2">
-        <v>0.001890572694437162</v>
+        <v>0.001890572694437155</v>
       </c>
       <c r="J2">
-        <v>0.0001890570689231013</v>
+        <v>0.0001890570689231924</v>
       </c>
       <c r="K2">
-        <v>0.001890570651055411</v>
+        <v>0.00189057065105539</v>
       </c>
       <c r="L2">
-        <v>0.0001890570689138442</v>
+        <v>0.0001890570689138394</v>
       </c>
       <c r="M2">
-        <v>0.001890570651039279</v>
+        <v>0.001890570651039273</v>
       </c>
       <c r="N2">
-        <v>0.5484829484561066</v>
+        <v>0.5484829484561268</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>0.5484829484574727</v>
+        <v>0.5484829484574892</v>
       </c>
       <c r="Q2">
-        <v>-2.097213048216355E-06</v>
+        <v>-2.09721410191716E-06</v>
       </c>
       <c r="R2">
         <v>0</v>
       </c>
       <c r="S2">
-        <v>179.999997902928</v>
+        <v>179.9999979029291</v>
       </c>
       <c r="T2">
-        <v>115.4699706704404</v>
+        <v>115.4699706704417</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -6885,22 +6885,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.5484829701491942</v>
+        <v>0.5484829701520553</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.5484830378616689</v>
+        <v>0.5484830378740623</v>
       </c>
       <c r="Q3">
-        <v>9.995301698560645E-06</v>
+        <v>9.993927093117185E-06</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>179.999989894159</v>
+        <v>179.9999898935524</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -6908,7 +6908,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -6947,22 +6947,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.5484829773802291</v>
+        <v>0.5484829773840498</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.5484830676630686</v>
+        <v>0.5484830676784415</v>
       </c>
       <c r="Q4">
-        <v>1.402613959026893E-05</v>
+        <v>1.40249445447088E-05</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.99998722457</v>
+        <v>179.9999872237933</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -6970,7 +6970,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -7009,22 +7009,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.5484829744878148</v>
+        <v>0.5484829744915224</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.5484830557425091</v>
+        <v>0.5484830557563996</v>
       </c>
       <c r="Q5">
-        <v>1.241380452537015E-05</v>
+        <v>1.241264011412788E-05</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9999882924056</v>
+        <v>179.9999882918291</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -7065,7 +7065,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0.0342865502553216</v>
@@ -7088,7 +7088,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -7111,7 +7111,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -7134,7 +7134,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -7229,69 +7229,69 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>115.4700366699536</v>
+        <v>115.4700366699553</v>
       </c>
       <c r="D2">
-        <v>115.47002973471</v>
+        <v>115.4700297347051</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>26.6666630992577</v>
+        <v>26.66666309925809</v>
       </c>
       <c r="G2">
-        <v>26.66666149763177</v>
+        <v>26.66666149763066</v>
       </c>
       <c r="H2">
-        <v>0.0001791070683994123</v>
+        <v>0.0001791070683994417</v>
       </c>
       <c r="I2">
-        <v>0.001791068766536983</v>
+        <v>0.001791068766536954</v>
       </c>
       <c r="J2">
-        <v>0.0001791066968295036</v>
+        <v>0.0001791066968295965</v>
       </c>
       <c r="K2">
-        <v>0.001791066932594685</v>
+        <v>0.00179106693259478</v>
       </c>
       <c r="L2">
-        <v>0.0001791066968172275</v>
+        <v>0.0001791066968171942</v>
       </c>
       <c r="M2">
-        <v>0.001791066932573329</v>
+        <v>0.001791066932573288</v>
       </c>
       <c r="N2">
-        <v>0.5196154076582286</v>
+        <v>0.5196154076582365</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>0.5196154076571319</v>
+        <v>0.5196154076571339</v>
       </c>
       <c r="Q2">
-        <v>-1.986859143373534E-06</v>
+        <v>-1.986860317002019E-06</v>
       </c>
       <c r="R2">
         <v>0</v>
       </c>
       <c r="S2">
-        <v>179.9999980131776</v>
+        <v>179.9999980131763</v>
       </c>
       <c r="T2">
-        <v>115.4699734839606</v>
+        <v>115.4699734839634</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -7330,22 +7330,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.5196154282095766</v>
+        <v>0.5196154282100653</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.5196154923558448</v>
+        <v>0.5196154923649065</v>
       </c>
       <c r="Q3">
-        <v>1.010565589571563E-05</v>
+        <v>1.010444160458941E-05</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>179.9999900044085</v>
+        <v>179.9999900045046</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -7353,7 +7353,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -7392,22 +7392,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.5196154350600314</v>
+        <v>0.5196154350611345</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.5196155205887503</v>
+        <v>0.5196155205959138</v>
       </c>
       <c r="Q4">
-        <v>1.413649388101226E-05</v>
+        <v>1.413535177172879E-05</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.9999873348195</v>
+        <v>179.9999873348881</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -7415,7 +7415,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -7454,22 +7454,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.5196154323198492</v>
+        <v>0.5196154323211397</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.5196155092955885</v>
+        <v>0.5196155093060685</v>
       </c>
       <c r="Q5">
-        <v>1.252415877600153E-05</v>
+        <v>1.252315467122144E-05</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.999988402655</v>
+        <v>179.9999884027813</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -7549,7 +7549,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -7570,22 +7570,22 @@
         <v>0.007163858920058049</v>
       </c>
       <c r="H2">
-        <v>0.0001890574829298326</v>
+        <v>0.0001890574829297745</v>
       </c>
       <c r="I2">
-        <v>0.001890572694437162</v>
+        <v>0.001890572694437155</v>
       </c>
       <c r="J2">
-        <v>0.0001890570689231013</v>
+        <v>0.0001890570689231924</v>
       </c>
       <c r="K2">
-        <v>0.001890570651055411</v>
+        <v>0.00189057065105539</v>
       </c>
       <c r="L2">
-        <v>0.0001890570689138442</v>
+        <v>0.0001890570689138394</v>
       </c>
       <c r="M2">
-        <v>0.001890570651039279</v>
+        <v>0.001890570651039273</v>
       </c>
       <c r="N2">
         <v>0.9499478656949593</v>
@@ -7611,7 +7611,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -7650,22 +7650,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9499478656956913</v>
+        <v>0.949947865695693</v>
       </c>
       <c r="O3">
-        <v>0.9498024508108096</v>
+        <v>0.9498024508108092</v>
       </c>
       <c r="P3">
-        <v>0.949854569745043</v>
+        <v>0.9498545697450441</v>
       </c>
       <c r="Q3">
         <v>29.99168765545167</v>
       </c>
       <c r="R3">
-        <v>-90.00974692478427</v>
+        <v>-90.00974692478421</v>
       </c>
       <c r="S3">
-        <v>149.9985667710396</v>
+        <v>149.9985667710397</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -7673,7 +7673,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -7712,22 +7712,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9499478656959355</v>
+        <v>0.9499478656959367</v>
       </c>
       <c r="O4">
-        <v>0.9498024508203063</v>
+        <v>0.9498024508203071</v>
       </c>
       <c r="P4">
-        <v>0.9498545697542967</v>
+        <v>0.9498545697542977</v>
       </c>
       <c r="Q4">
-        <v>29.99168765608761</v>
+        <v>29.99168765608768</v>
       </c>
       <c r="R4">
-        <v>-90.00974692384294</v>
+        <v>-90.00974692384287</v>
       </c>
       <c r="S4">
-        <v>149.9985667713447</v>
+        <v>149.9985667713449</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -7735,7 +7735,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -7774,22 +7774,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9499478656958379</v>
+        <v>0.9499478656958404</v>
       </c>
       <c r="O5">
         <v>0.9498024508165076</v>
       </c>
       <c r="P5">
-        <v>0.9498545697505951</v>
+        <v>0.9498545697505963</v>
       </c>
       <c r="Q5">
-        <v>29.99168765583323</v>
+        <v>29.99168765583328</v>
       </c>
       <c r="R5">
-        <v>-90.00974692421947</v>
+        <v>-90.00974692421944</v>
       </c>
       <c r="S5">
-        <v>149.9985667712227</v>
+        <v>149.9985667712229</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -7869,7 +7869,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -7884,28 +7884,28 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.006786887898418491</v>
+        <v>0.006786887898418493</v>
       </c>
       <c r="G2">
         <v>0.006786887898991262</v>
       </c>
       <c r="H2">
-        <v>0.0001791070683994123</v>
+        <v>0.0001791070683994417</v>
       </c>
       <c r="I2">
-        <v>0.001791068766536983</v>
+        <v>0.001791068766536954</v>
       </c>
       <c r="J2">
-        <v>0.0001791066968295036</v>
+        <v>0.0001791066968295965</v>
       </c>
       <c r="K2">
-        <v>0.001791066932594685</v>
+        <v>0.00179106693259478</v>
       </c>
       <c r="L2">
-        <v>0.0001791066968172275</v>
+        <v>0.0001791066968171942</v>
       </c>
       <c r="M2">
-        <v>0.001791066932573329</v>
+        <v>0.001791066932573288</v>
       </c>
       <c r="N2">
         <v>0.8999531960812501</v>
@@ -7931,7 +7931,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -7970,22 +7970,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8999531960819072</v>
+        <v>0.8999531960819085</v>
       </c>
       <c r="O3">
-        <v>0.8998226838031753</v>
+        <v>0.8998226838031719</v>
       </c>
       <c r="P3">
-        <v>0.8998694609465716</v>
+        <v>0.8998694609465704</v>
       </c>
       <c r="Q3">
-        <v>29.99212505716115</v>
+        <v>29.99212505716119</v>
       </c>
       <c r="R3">
-        <v>-90.0092340298015</v>
+        <v>-90.00923402980146</v>
       </c>
       <c r="S3">
-        <v>149.9986421258307</v>
+        <v>149.9986421258311</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -7993,7 +7993,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -8032,22 +8032,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8999531960821263</v>
+        <v>0.8999531960821276</v>
       </c>
       <c r="O4">
-        <v>0.8998226838116987</v>
+        <v>0.8998226838116957</v>
       </c>
       <c r="P4">
-        <v>0.8998694609548769</v>
+        <v>0.8998694609548746</v>
       </c>
       <c r="Q4">
-        <v>29.99212505776362</v>
+        <v>29.99212505776371</v>
       </c>
       <c r="R4">
         <v>-90.00923402890973</v>
       </c>
       <c r="S4">
-        <v>149.9986421261199</v>
+        <v>149.9986421261201</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -8055,7 +8055,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -8094,22 +8094,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8999531960820387</v>
+        <v>0.8999531960820409</v>
       </c>
       <c r="O5">
-        <v>0.8998226838082894</v>
+        <v>0.8998226838082863</v>
       </c>
       <c r="P5">
-        <v>0.8998694609515548</v>
+        <v>0.8998694609515536</v>
       </c>
       <c r="Q5">
-        <v>29.99212505752263</v>
+        <v>29.9921250575227</v>
       </c>
       <c r="R5">
-        <v>-90.00923402926645</v>
+        <v>-90.00923402926644</v>
       </c>
       <c r="S5">
-        <v>149.9986421260042</v>
+        <v>149.9986421260046</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -8150,7 +8150,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0.03591893103464823</v>
@@ -8173,7 +8173,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -8196,7 +8196,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -8219,7 +8219,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -8275,7 +8275,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>115.4700547192921</v>
@@ -8298,7 +8298,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -8321,7 +8321,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -8344,7 +8344,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -8400,7 +8400,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>115.4700531090195</v>
@@ -8423,7 +8423,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -8446,7 +8446,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -8469,7 +8469,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -8525,7 +8525,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0.03102041860706187</v>
@@ -8548,7 +8548,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -8571,7 +8571,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -8594,7 +8594,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -8650,7 +8650,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0.02938808622774167</v>
@@ -8673,7 +8673,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -8696,7 +8696,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -8719,7 +8719,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -8811,66 +8811,66 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>124.9999968460333</v>
+        <v>124.9999968460335</v>
       </c>
       <c r="D2">
-        <v>124.9999968460333</v>
+        <v>124.9999968460335</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>28.86751316126333</v>
+        <v>28.86751316126339</v>
       </c>
       <c r="G2">
-        <v>28.86751316126333</v>
+        <v>28.86751316126339</v>
       </c>
       <c r="H2">
-        <v>0.0001671665735633938</v>
+        <v>0.0001671665735633701</v>
       </c>
       <c r="I2">
-        <v>0.001671664068087942</v>
+        <v>0.001671664068087988</v>
       </c>
       <c r="J2">
-        <v>0.0001671662503029855</v>
+        <v>0.0001671662503028824</v>
       </c>
       <c r="K2">
-        <v>0.001671662470403454</v>
+        <v>0.001671662470403327</v>
       </c>
       <c r="L2">
-        <v>0.0001671662503084033</v>
+        <v>0.000167166250308345</v>
       </c>
       <c r="M2">
-        <v>0.001671662470412751</v>
+        <v>0.001671662470412701</v>
       </c>
       <c r="N2">
-        <v>0.9093266326847956</v>
+        <v>0.9093266326847831</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>0.9093266326841557</v>
+        <v>0.909326632684141</v>
       </c>
       <c r="Q2">
-        <v>2.130429580670691E-11</v>
+        <v>2.158915219487852E-11</v>
       </c>
       <c r="R2">
         <v>0</v>
       </c>
       <c r="S2">
-        <v>179.99999999997</v>
+        <v>179.9999999999705</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -8909,27 +8909,27 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9093265952654933</v>
+        <v>0.9093265952674874</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.9093266701034617</v>
+        <v>0.9093266700986808</v>
       </c>
       <c r="Q3">
-        <v>3.489829750879405E-06</v>
+        <v>3.489889847900504E-06</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>179.9999965101618</v>
+        <v>179.9999965107781</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -8968,27 +8968,27 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9093265827923936</v>
+        <v>0.9093265827948738</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.909326682576564</v>
+        <v>0.909326682569395</v>
       </c>
       <c r="Q4">
-        <v>4.653099288392024E-06</v>
+        <v>4.653115798909158E-06</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.9999953468925</v>
+        <v>179.9999953474818</v>
       </c>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -9027,22 +9027,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9093265877816331</v>
+        <v>0.9093265877830814</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.9093266775873233</v>
+        <v>0.9093266775791948</v>
       </c>
       <c r="Q5">
-        <v>4.187791480058322E-06</v>
+        <v>4.18783914987504E-06</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9999958122002</v>
+        <v>179.999995813018</v>
       </c>
     </row>
   </sheetData>
